--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5FE23E-CC30-41DB-A9A3-BE516EF4152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF89153C-4EBE-4735-8F5C-F160D3CBF39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-75" windowWidth="25440" windowHeight="15270" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32355" yWindow="345" windowWidth="25170" windowHeight="15000" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,9 @@
     <sheet name="CoreMeta4Cat" sheetId="3" r:id="rId3"/>
     <sheet name="Synthesis" sheetId="4" r:id="rId4"/>
     <sheet name="Characterization" sheetId="5" r:id="rId5"/>
-    <sheet name="Reaction" sheetId="6" r:id="rId6"/>
-    <sheet name="Simulation" sheetId="7" r:id="rId7"/>
+    <sheet name="Reaction_original" sheetId="8" r:id="rId6"/>
+    <sheet name="Reaction" sheetId="6" r:id="rId7"/>
+    <sheet name="Simulation" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5324" uniqueCount="1385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5250" uniqueCount="1244">
   <si>
     <t>CoreMeta4Cat Vocabulary Reference Workbook</t>
   </si>
@@ -2716,6 +2717,38 @@
 The abstract stub ProductIdentificationMethod is retained for backward compatibility.</t>
   </si>
   <si>
+    <t>Abstract Plan representing the method used to identify and quantify reaction
+products. In practice, users should reference a concrete CharacterizationTechnique
+subclass from coremeta4cat_characterization_ap (e.g. GCMS, HPLC_MS, NMRSpectroscopy).
+This abstract class is retained for backward compatibility with the original
+CoreMeta4Cat monolith. It is a subclass of Plan (prov:Plan / OBI:0000272) so that
+it can participate in the realized_plan slot if needed.</t>
+  </si>
+  <si>
+    <t>carried out by</t>
+  </si>
+  <si>
+    <t>ChemicalReactor</t>
+  </si>
+  <si>
+    <t>The reactor in which the Reaction takes place.
+Must be a Reactor instance (a Device subclass specific to catalytic
+reaction vessels, e.g. FixedBedReactor, CSTR, Autoclave).</t>
+  </si>
+  <si>
+    <t>VOC4CAT:0007018</t>
+  </si>
+  <si>
+    <t>Abstract Device subclass representing a catalytic reactor vessel.
+Reactor is more specific than the general Device (AgenticEntity): it restricts
+carried_out_by on Reaction to dedicated reactor equipment. This semantic
+distinction separates analytical instruments (Device) from reaction vessels
+(Reactor) in the carried_out_by relationship.
+Concrete subclasses (FixedBedReactor, CSTR, PlugFlowReactor, …) specify
+reactor geometry and operating mode.
+Linked from Reaction via carried_out_by (restricted to range: Reactor).</t>
+  </si>
+  <si>
     <t>ElectrochemicalReactor</t>
   </si>
   <si>
@@ -3841,252 +3874,6 @@
     <t>Interval between successive MC snapshots used for property averaging.</t>
   </si>
   <si>
-    <t>reaction type</t>
-  </si>
-  <si>
-    <t>voc4cat:0007010</t>
-  </si>
-  <si>
-    <t>A group of chemical reactions with common conditions or reactants, e.g. Oxidation, Hydrogenation, Reduction, Cracking.</t>
-  </si>
-  <si>
-    <t>hydrogenation</t>
-  </si>
-  <si>
-    <t>voc4cat:0000260</t>
-  </si>
-  <si>
-    <t>A chemical reaction of molecular hydrogen (H2) and another chemical species, typically facilitated by a catalyst.</t>
-  </si>
-  <si>
-    <t>oxidation</t>
-  </si>
-  <si>
-    <t>voc4cat:0000097</t>
-  </si>
-  <si>
-    <t>The loss of electrons or an increase in the oxidation state of a species.</t>
-  </si>
-  <si>
-    <t>dehydrogenation</t>
-  </si>
-  <si>
-    <t>voc4cat:0000297</t>
-  </si>
-  <si>
-    <t>A chemical reaction that involves the removal of two or more hydrogen atoms from a molecule.</t>
-  </si>
-  <si>
-    <t>events</t>
-  </si>
-  <si>
-    <t>voc4cat:0000183</t>
-  </si>
-  <si>
-    <t>An occurrence or happening, marked by a specific point in time. Events can be observed, recorded, and may have an impact on the state of the system or entities involved.</t>
-  </si>
-  <si>
-    <t>C-C coupling reaction</t>
-  </si>
-  <si>
-    <t>voc4cat:0000223</t>
-  </si>
-  <si>
-    <t>A chemical reaction where a carbon-carbon bond is formed from two carbon-containing fragments.</t>
-  </si>
-  <si>
-    <t>hydrodeoxygenation</t>
-  </si>
-  <si>
-    <t>voc4cat:0000226</t>
-  </si>
-  <si>
-    <t>A catalytic process in which oxygen is removed from oxygenated organic compounds using hydrogen.</t>
-  </si>
-  <si>
-    <t>oxygen evolution reaction</t>
-  </si>
-  <si>
-    <t>voc4cat:0000236</t>
-  </si>
-  <si>
-    <t>A chemical reaction of generating molecular oxygen in electrochemistry.</t>
-  </si>
-  <si>
-    <t>carbonylation</t>
-  </si>
-  <si>
-    <t>voc4cat:0000247</t>
-  </si>
-  <si>
-    <t>A chemical reaction in which a carbonyl group (C=O) is introduced into a molecule, typically through the addition of carbon monoxide (CO) to a substrate.</t>
-  </si>
-  <si>
-    <t>hydroxylation</t>
-  </si>
-  <si>
-    <t>voc4cat:0000258</t>
-  </si>
-  <si>
-    <t>The addition of a hydroxyl group (-OH) to a molecule, typically by replacing a hydrogen atom.</t>
-  </si>
-  <si>
-    <t>CO2 hydrogenation</t>
-  </si>
-  <si>
-    <t>voc4cat:0000259</t>
-  </si>
-  <si>
-    <t>The reaction of carbon dioxide (CO2) with molecular hydrogen (H2) to produce value-added hydrocarbons or alcohols.</t>
-  </si>
-  <si>
-    <t>selective oxidation</t>
-  </si>
-  <si>
-    <t>voc4cat:0000261</t>
-  </si>
-  <si>
-    <t>The targeted oxidation of a specific bond or functional group in a molecule leaving other sites unaffected, often directed by a catalyst.</t>
-  </si>
-  <si>
-    <t>Fischer-Tropsch synthesis</t>
-  </si>
-  <si>
-    <t>voc4cat:0000280</t>
-  </si>
-  <si>
-    <t>A catalytic chemical reaction in which a mixture of carbon monoxide (CO) and hydrogen (H2), is converted via a chain-growth mechanism into long-chain hydrocarbons (e.g., alkanes, alkenes or alcohols)—typically using iron or cobalt catalysts under moderate to high pressures and temperatures.</t>
-  </si>
-  <si>
-    <t>CO oxidation</t>
-  </si>
-  <si>
-    <t>voc4cat:0000289</t>
-  </si>
-  <si>
-    <t>The reaction in which carbon monoxide (CO) is converted to carbon dioxide (CO₂) through interaction with an oxidizing agent, typically oxygen (O₂).</t>
-  </si>
-  <si>
-    <t>heterogeneous catalyst</t>
-  </si>
-  <si>
-    <t>voc4cat:0007003</t>
-  </si>
-  <si>
-    <t>A substance that increases the rate of a chemical reaction that is in a different phase than the reagents.</t>
-  </si>
-  <si>
-    <t>thin film</t>
-  </si>
-  <si>
-    <t>voc4cat:0000019</t>
-  </si>
-  <si>
-    <t>A catalyst introduced to the reaction chamber in the form of a thin film. To form a thin film, a (powdered) catalyst is deposited on a substrate (e.g., glass or metal) using an appropriate deposition technique.</t>
-  </si>
-  <si>
-    <t>bulk catalyst</t>
-  </si>
-  <si>
-    <t>voc4cat:0007015</t>
-  </si>
-  <si>
-    <t>A catalyst that consists mainly of the active ingredient or phase.</t>
-  </si>
-  <si>
-    <t>powdered catalyst</t>
-  </si>
-  <si>
-    <t>voc4cat:0000017</t>
-  </si>
-  <si>
-    <t>A catalyst introduced to the reaction chamber in the form of a powder.</t>
-  </si>
-  <si>
-    <t>deposited sample</t>
-  </si>
-  <si>
-    <t>voc4cat:0000038</t>
-  </si>
-  <si>
-    <t>A thin film of the catalyst deposited on an appropriate for the application substrate.</t>
-  </si>
-  <si>
-    <t>electrocatalyst</t>
-  </si>
-  <si>
-    <t>voc4cat:0000254</t>
-  </si>
-  <si>
-    <t>A material which directs and accelerates an electrochemical reaction while remaining unchanged in the process.</t>
-  </si>
-  <si>
-    <t>photocatalyst</t>
-  </si>
-  <si>
-    <t>voc4cat:0000002</t>
-  </si>
-  <si>
-    <t>A material that absorbs photons (light) of appropriate energy and initiates or accelerates a photochemical reaction, while it regenerates itself after each reaction cycle.</t>
-  </si>
-  <si>
-    <t>supported catalyst</t>
-  </si>
-  <si>
-    <t>voc4cat:0007034</t>
-  </si>
-  <si>
-    <t>A catalyst where the active material is usually the minority phase and fixed on a high surface area, relatively inert solid.</t>
-  </si>
-  <si>
-    <t>liquid phase analysis</t>
-  </si>
-  <si>
-    <t>voc4cat:0007813</t>
-  </si>
-  <si>
-    <t>Analysis of the liquid sample from a catalytic test.</t>
-  </si>
-  <si>
-    <t>gas phase analysis</t>
-  </si>
-  <si>
-    <t>voc4cat:0007814</t>
-  </si>
-  <si>
-    <t>Analysis of the gaseous sample from a catalytic test.</t>
-  </si>
-  <si>
-    <t>Chromatographic Methods</t>
-  </si>
-  <si>
-    <t>Gas Chromatography (GC)</t>
-  </si>
-  <si>
-    <t>Gas Chromatography–Mass Spectrometry (GC-MS)</t>
-  </si>
-  <si>
-    <t>High Performance Liquid Chromatography (HPLC)</t>
-  </si>
-  <si>
-    <t>Spectroscopic Methods</t>
-  </si>
-  <si>
-    <t>Mass Spectrometry (MS)</t>
-  </si>
-  <si>
-    <t>Fourier Transform Infrared Spectroscopy (FTIR)</t>
-  </si>
-  <si>
-    <t>reactor design type</t>
-  </si>
-  <si>
-    <t>voc4cat:0007018</t>
-  </si>
-  <si>
-    <t>A classification of chemical reactors based on the distinct design, configuration, and operational characteristics. Examples are stirred tank reactors, loop reactors, trickle beds, multitubular reactors, fluidized beds, and others. Each type is tailored to accomodate a specific combinations of reaction kinetics, thermodynamics, mass transfer requirements, and process variables.</t>
-  </si>
-  <si>
     <t>cathode</t>
   </si>
   <si>
@@ -4142,209 +3929,13 @@
   </si>
   <si>
     <t>The current that is flowing through an electrochemical cell and is causing (or is caused by) chemical reactions (charge transfer) occurring at the electrode surfaces.</t>
-  </si>
-  <si>
-    <t>stirring rate</t>
-  </si>
-  <si>
-    <t>voc4cat:0008114</t>
-  </si>
-  <si>
-    <t>The rate at which the stirrer rotates, typically expressed in revolutions per unit time (e.g. revolutions or rotations per minute, rpm).</t>
-  </si>
-  <si>
-    <t>residence time</t>
-  </si>
-  <si>
-    <t>reactor working volume</t>
-  </si>
-  <si>
-    <t>voc4cat:0000153</t>
-  </si>
-  <si>
-    <t>Volume of the reaction chamber, calculated by its dimensions.</t>
-  </si>
-  <si>
-    <t>reactor diameter</t>
-  </si>
-  <si>
-    <t>tube length</t>
-  </si>
-  <si>
-    <t>tube internal diameter</t>
-  </si>
-  <si>
-    <t>flow direction</t>
-  </si>
-  <si>
-    <t>catalyst particle size</t>
-  </si>
-  <si>
-    <t>voc4cat:0008212</t>
-  </si>
-  <si>
-    <t>A measure of the characteristic linear dimension of a particle in a sample, typically reported as diameter, equivalent diameter, or another size metric determined by an appropriate measurement method.</t>
-  </si>
-  <si>
-    <t>agitation type</t>
-  </si>
-  <si>
-    <t>reaction chamber material</t>
-  </si>
-  <si>
-    <t>voc4cat:0000156</t>
-  </si>
-  <si>
-    <t>Material used for the construction of the main body of the reaction chamber.</t>
-  </si>
-  <si>
-    <t>experiment duration</t>
-  </si>
-  <si>
-    <t>voc4cat:0000111</t>
-  </si>
-  <si>
-    <t>The total duration of an experiment.</t>
-  </si>
-  <si>
-    <t>gas-liquid ratio</t>
-  </si>
-  <si>
-    <t>agitation/sparging rate</t>
-  </si>
-  <si>
-    <t>channel dimensions</t>
-  </si>
-  <si>
-    <t>number of channels</t>
-  </si>
-  <si>
-    <t>catalyst bed volume</t>
-  </si>
-  <si>
-    <t>voc4cat:0007021</t>
-  </si>
-  <si>
-    <t>The bulk volume taken up by the catalyst and potential diluent in a fixed bed reactor.</t>
-  </si>
-  <si>
-    <t>catalyst dilution material</t>
-  </si>
-  <si>
-    <t>voc4cat:0008218</t>
-  </si>
-  <si>
-    <t>An inert solid mixed with catalyst particles in a fixed bed to modify bed properties (e.g., improve heat transfer, hydrodynamics).</t>
-  </si>
-  <si>
-    <t>catalyst bed height</t>
-  </si>
-  <si>
-    <t>voc4cat:0008217</t>
-  </si>
-  <si>
-    <t>The axial length of the packed catalyst section in a reactor, measured along the direction of flow between the defined bed boundaries.</t>
-  </si>
-  <si>
-    <t>reaction conditions</t>
-  </si>
-  <si>
-    <t>reactor feed</t>
-  </si>
-  <si>
-    <t>voc4cat:0007004</t>
-  </si>
-  <si>
-    <t>The composition of chemical species fed to the inlet of a chemical reactor.</t>
-  </si>
-  <si>
-    <t>reaction temperature</t>
-  </si>
-  <si>
-    <t>voc4cat:0007013</t>
-  </si>
-  <si>
-    <t>The temperature at which a chemical reaction is happening.</t>
-  </si>
-  <si>
-    <t>gas hourly space velocity</t>
-  </si>
-  <si>
-    <t>voc4cat:0007023</t>
-  </si>
-  <si>
-    <t>A physical quantity given by the volumetric flow entering a control volume divided by the size of the control volume; the quantity must be given in the unit 1/hour.  In heterogeneous catalysis the volume of the undiluted catalyst bed is used as characteristic control volume. In case of gases the flow at reference conditions (0°C, 100 kPa = 1 bar) is used.</t>
-  </si>
-  <si>
-    <t>weight hourly space velocity</t>
-  </si>
-  <si>
-    <t>voc4cat:0007046</t>
-  </si>
-  <si>
-    <t>A physical quantity given by the volumetric flow entering a catalytic reactor divided by the mass of the undiluted catalyst bed in this control volume. In case of gases the flow at reference conditions (0°C, 100 kPa = 1 bar) is used.</t>
-  </si>
-  <si>
-    <t>reaction name</t>
-  </si>
-  <si>
-    <t>voc4cat:0007009</t>
-  </si>
-  <si>
-    <t>A name for a chemical reaction which assigns the reactants and (desired) products.</t>
-  </si>
-  <si>
-    <t>reactor performance measure</t>
-  </si>
-  <si>
-    <t>voc4cat:0005001</t>
-  </si>
-  <si>
-    <t>A measure to quantify how fast and selective a chemical conversion occurs in a reactor. A chemical conversion may include multiple reactions.</t>
-  </si>
-  <si>
-    <t>conversion</t>
-  </si>
-  <si>
-    <t>voc4cat:0005004</t>
-  </si>
-  <si>
-    <t>A dimensionless physical quantity describing the fraction of a reactant that reacts in a chemical conversion. If a reactant is consumed completely its conversion is 1 (or 100 %).</t>
-  </si>
-  <si>
-    <t>yield</t>
-  </si>
-  <si>
-    <t>voc4cat:0005005</t>
-  </si>
-  <si>
-    <t>A dimensionless physical quantity describing the fraction of a product B that is formed from a reactant A taking into account the stoichiometry. If A fully reacts to B without side-reactions, the yield of product B is 1 (or 100 %).</t>
-  </si>
-  <si>
-    <t>space-time yield</t>
-  </si>
-  <si>
-    <t>voc4cat:0005006</t>
-  </si>
-  <si>
-    <t>A physical quantity that describes the amount of product produced per unit of time and unit of producing entity. The producing entity is for example the volume of a chemical reactor or in catalysis the mass or volume or moles of catalyst.
-Example unit: kg{product} / (hour * cubicmeter{catalyst})</t>
-  </si>
-  <si>
-    <t>selectivity</t>
-  </si>
-  <si>
-    <t>voc4cat:0000125</t>
-  </si>
-  <si>
-    <t>A dimensionless physical quantity describing how effective a reactant is converted to the desired product in a chemical conversion. It is calculated as the ratio between the amount of the desired product and the amount of the desired product that could have been formed if all reactants were converted to the desired product. The selectivity is 1 (or 100 %) if no other than the desired product is formed.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4378,12 +3969,12 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -4395,21 +3986,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0563C1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4463,18 +4041,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -4484,16 +4068,76 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
       </left>
       <right/>
       <top style="thin">
@@ -4505,8 +4149,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
       <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </top>
@@ -4519,7 +4167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -4554,63 +4202,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -4621,136 +4212,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E79"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4761,25 +4265,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{309C24BC-0679-45A9-9C93-3A85E385EB7C}" name="Table1" displayName="Table1" ref="A1:J93" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J93" xr:uid="{309C24BC-0679-45A9-9C93-3A85E385EB7C}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B7D71E55-01D3-48E2-A80C-82F021F9057F}" name="label" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{FBD6A85E-4A77-4CD1-BFD8-BFBFD95E5CE7}" name="type" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{2250F21D-B2CF-4D58-BD20-1B765788C2EA}" name="domain" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{F6A59460-B79A-49B9-A5B4-AB4B204DA480}" name="M / R / O" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{BFFD251B-F1C7-4702-89AE-519CFA02633D}" name="range" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{32E19823-E9A5-440A-9DCE-D91A066AA9E4}" name="multivalued" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{A2E07E2A-417E-4269-9EDD-5C5282D499A0}" name="inlined as list" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{D3774FBC-E936-46C7-9AEA-1F334CCDA8F6}" name="unit" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{1E12EE40-5FCF-4042-B9D7-95FC17D754D4}" name="uri" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{2D06B9DD-A773-40EB-B129-0BF1F1E3ED3B}" name="description" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5075,17 +4560,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="13"/>
     </row>
     <row r="4" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -5121,10 +4606,10 @@
     </row>
     <row r="8" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="32"/>
+      <c r="B9" s="13"/>
     </row>
     <row r="10" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -5184,10 +4669,10 @@
     </row>
     <row r="17" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="32"/>
+      <c r="B18" s="13"/>
     </row>
     <row r="19" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -5291,19 +4776,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
     </row>
     <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -5340,11 +4825,11 @@
     </row>
     <row r="7" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
     </row>
     <row r="9" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -5428,18 +4913,18 @@
     </row>
     <row r="19" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
     </row>
     <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -18838,8 +18323,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J93"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4241D815-8C04-4064-89DE-57B4438C4484}">
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -18855,386 +18340,432 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="15" t="s">
-        <v>1220</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>1222</v>
-      </c>
-      <c r="B3" s="14" t="s">
+      <c r="C6" s="11" t="s">
+        <v>861</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="18" t="s">
-        <v>1223</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="C10" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="18" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="C11" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B6" s="14" t="s">
+      <c r="C14" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="21" t="s">
-        <v>1232</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="18" t="s">
-        <v>1235</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="18" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="18" t="s">
-        <v>1241</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="17" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="18" t="s">
-        <v>1244</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="17" t="s">
-        <v>1246</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="18" t="s">
-        <v>1247</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
-        <v>1249</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="18" t="s">
-        <v>1250</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="17" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="18" t="s">
-        <v>1253</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="17" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="18" t="s">
-        <v>1256</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="17" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="18" t="s">
-        <v>1259</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>852</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9" t="s">
-        <v>853</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>854</v>
+      <c r="C16" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>96</v>
+        <v>871</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>74</v>
@@ -19244,1771 +18775,1229 @@
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="8" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>880</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11" t="s">
+        <v>884</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
+        <v>886</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11" t="s">
+        <v>887</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>889</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11" t="s">
+        <v>890</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>892</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
+        <v>904</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8" t="s">
-        <v>859</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
-        <v>1261</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="18" t="s">
-        <v>1262</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A20" s="17" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="18" t="s">
-        <v>1265</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="18" t="s">
-        <v>1268</v>
-      </c>
-      <c r="J21" s="19" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="17" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="18" t="s">
-        <v>1271</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="17" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="18" t="s">
-        <v>1274</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="s">
-        <v>1276</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="18" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="22" t="s">
-        <v>1279</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="18" t="s">
-        <v>1280</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="17" t="s">
-        <v>1282</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="18" t="s">
-        <v>1283</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="J28" s="23" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="J29" s="23" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>871</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="17" t="s">
-        <v>1285</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="18" t="s">
-        <v>1286</v>
-      </c>
-      <c r="J31" s="19" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" s="17" t="s">
-        <v>1288</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="18" t="s">
-        <v>1289</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="14"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>1292</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="14"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="14"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="14"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="14"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>1296</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="14"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>1297</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="14"/>
-    </row>
-    <row r="40" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A40" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23" t="s">
-        <v>1299</v>
-      </c>
-      <c r="J40" s="23" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="23" t="s">
-        <v>874</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23" t="s">
-        <v>875</v>
-      </c>
-      <c r="J41" s="23" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
-        <v>1301</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>874</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9" t="s">
-        <v>1302</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>874</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A44" s="24" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>874</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24" t="s">
-        <v>1308</v>
-      </c>
-      <c r="J44" s="24" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="25" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>874</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25" t="s">
-        <v>1311</v>
-      </c>
-      <c r="J45" s="25" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>1313</v>
-      </c>
-      <c r="B46" t="s">
-        <v>103</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>1307</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>1314</v>
-      </c>
-      <c r="J46" s="16" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>1316</v>
-      </c>
-      <c r="B47" t="s">
-        <v>103</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>1317</v>
-      </c>
-      <c r="B48" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>874</v>
-      </c>
-      <c r="D48" t="s">
-        <v>51</v>
-      </c>
-      <c r="I48" s="26" t="s">
-        <v>1318</v>
-      </c>
-      <c r="J48" s="27" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="25" t="s">
-        <v>877</v>
-      </c>
-      <c r="B49" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23" t="s">
-        <v>878</v>
-      </c>
-      <c r="J49" s="23" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A50" s="25" t="s">
-        <v>1320</v>
-      </c>
-      <c r="B50" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>877</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="25"/>
-      <c r="I50" t="s">
-        <v>1321</v>
-      </c>
-      <c r="J50" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A51" s="25" t="s">
-        <v>1323</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>877</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="25"/>
-      <c r="I51" s="25"/>
-      <c r="J51" s="25"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A52" s="25" t="s">
-        <v>1324</v>
-      </c>
-      <c r="B52" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>877</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="25"/>
-      <c r="I52" t="s">
-        <v>1325</v>
-      </c>
-      <c r="J52" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A53" s="25" t="s">
-        <v>1327</v>
-      </c>
-      <c r="B53" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>877</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-    </row>
-    <row r="54" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="23" t="s">
-        <v>880</v>
-      </c>
-      <c r="B54" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="23" t="s">
-        <v>881</v>
-      </c>
-      <c r="J54" s="23" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A55" s="25" t="s">
-        <v>1328</v>
-      </c>
-      <c r="B55" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>880</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-      <c r="J55" s="25"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A56" s="25" t="s">
-        <v>1329</v>
-      </c>
-      <c r="B56" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>880</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
-      <c r="I56" s="25"/>
-      <c r="J56" s="25"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A57" s="25" t="s">
-        <v>1330</v>
-      </c>
-      <c r="B57" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>880</v>
-      </c>
-      <c r="D57" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="25"/>
-      <c r="J57" s="25"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A58" s="25" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B58" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>880</v>
-      </c>
-      <c r="D58" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="25"/>
-      <c r="I58" t="s">
-        <v>1332</v>
-      </c>
-      <c r="J58" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A59" s="23" t="s">
-        <v>883</v>
-      </c>
-      <c r="B59" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C59" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="23" t="s">
-        <v>884</v>
-      </c>
-      <c r="J59" s="23" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B60" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>883</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="25"/>
-      <c r="J60" s="25"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>1335</v>
-      </c>
-      <c r="B61" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>883</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" t="s">
-        <v>1336</v>
-      </c>
-      <c r="J61" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>1338</v>
-      </c>
-      <c r="B62" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>883</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" t="s">
-        <v>1339</v>
-      </c>
-      <c r="J62" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="23" t="s">
-        <v>886</v>
-      </c>
-      <c r="B63" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C63" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="23"/>
-      <c r="I63" s="23" t="s">
-        <v>887</v>
-      </c>
-      <c r="J63" s="23" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A64" s="25" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B64" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="23" t="s">
-        <v>886</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
-      <c r="I64" t="s">
-        <v>1332</v>
-      </c>
-      <c r="J64" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>1341</v>
-      </c>
-      <c r="B65" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="23" t="s">
-        <v>886</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="25"/>
-      <c r="J65" s="25"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>1342</v>
-      </c>
-      <c r="B66" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>886</v>
-      </c>
-      <c r="D66" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="25"/>
-    </row>
-    <row r="67" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="23" t="s">
-        <v>889</v>
-      </c>
-      <c r="B67" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D67" s="23"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="23"/>
-      <c r="H67" s="23"/>
-      <c r="I67" s="23" t="s">
-        <v>890</v>
-      </c>
-      <c r="J67" s="23" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A68" s="25" t="s">
-        <v>1343</v>
-      </c>
-      <c r="B68" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>889</v>
-      </c>
-      <c r="D68" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="25"/>
-      <c r="J68" s="25"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A69" s="25" t="s">
-        <v>1344</v>
-      </c>
-      <c r="B69" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" s="23" t="s">
-        <v>889</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="25"/>
-      <c r="J69" s="25"/>
-    </row>
-    <row r="70" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="23" t="s">
-        <v>892</v>
-      </c>
-      <c r="B70" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C70" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23" t="s">
-        <v>893</v>
-      </c>
-      <c r="J70" s="23" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A71" s="25" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B71" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C71" s="23" t="s">
-        <v>892</v>
-      </c>
-      <c r="D71" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
-      <c r="I71" t="s">
-        <v>1332</v>
-      </c>
-      <c r="J71" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A72" s="24" t="s">
-        <v>1345</v>
-      </c>
-      <c r="B72" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C72" s="23" t="s">
-        <v>892</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
-      <c r="H72" s="25"/>
-      <c r="I72" s="15" t="s">
-        <v>1346</v>
-      </c>
-      <c r="J72" s="16" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A73" s="20" t="s">
-        <v>1348</v>
-      </c>
-      <c r="B73" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>892</v>
-      </c>
-      <c r="D73" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
-      <c r="I73" t="s">
-        <v>1349</v>
-      </c>
-      <c r="J73" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A74" s="20" t="s">
-        <v>1351</v>
-      </c>
-      <c r="B74" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C74" s="23" t="s">
-        <v>892</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="25"/>
-      <c r="I74" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J74" s="14" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A75" s="23" t="s">
-        <v>895</v>
-      </c>
-      <c r="B75" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C75" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23" t="s">
-        <v>896</v>
-      </c>
-      <c r="J75" s="23" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A76" s="10" t="s">
-        <v>898</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>895</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E76" s="10" t="s">
+      <c r="F29" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10" t="s">
+        <v>905</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
+        <v>907</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>908</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F76" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10" t="s">
-        <v>899</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A77" s="10" t="s">
-        <v>901</v>
-      </c>
-      <c r="B77" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>895</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F77" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10" t="s">
-        <v>682</v>
-      </c>
-      <c r="I77" s="10" t="s">
-        <v>902</v>
-      </c>
-      <c r="J77" s="10" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A78" s="10" t="s">
-        <v>904</v>
-      </c>
-      <c r="B78" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>895</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10" t="s">
-        <v>905</v>
-      </c>
-      <c r="J78" s="10" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A79" s="28" t="s">
-        <v>1354</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A80" s="10" t="s">
-        <v>864</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C80" s="28" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="F80" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H80" s="10"/>
-      <c r="I80" s="10" t="s">
-        <v>865</v>
-      </c>
-      <c r="J80" s="10" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A81" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C81" s="28" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="J81" s="10" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A82" s="28" t="s">
-        <v>1355</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C82" s="28" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D82" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="29" t="s">
-        <v>1356</v>
-      </c>
-      <c r="J82" s="30" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A83" s="28" t="s">
-        <v>1358</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C83" s="28" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="29" t="s">
-        <v>1359</v>
-      </c>
-      <c r="J83" s="30" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A84" s="10" t="s">
-        <v>861</v>
-      </c>
-      <c r="B84" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C84" s="28" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F84" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H84" s="10"/>
-      <c r="I84" s="10" t="s">
-        <v>862</v>
-      </c>
-      <c r="J84" s="10" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A85" s="10" t="s">
-        <v>867</v>
-      </c>
-      <c r="B85" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C85" s="28" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F85" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10" t="s">
-        <v>868</v>
-      </c>
-      <c r="J85" s="10" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A86" s="28" t="s">
-        <v>1361</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C86" s="28" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="29" t="s">
-        <v>1362</v>
-      </c>
-      <c r="J86" s="30" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A87" s="13" t="s">
-        <v>1364</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C87" s="28" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D87" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
-      <c r="I87" s="15" t="s">
-        <v>1365</v>
-      </c>
-      <c r="J87" s="16" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A88" s="13" t="s">
-        <v>1367</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="14"/>
-      <c r="I88" s="26" t="s">
-        <v>1368</v>
-      </c>
-      <c r="J88" s="27" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A89" s="28" t="s">
-        <v>1370</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C89" s="28"/>
-      <c r="D89" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="14"/>
-      <c r="H89" s="14"/>
-      <c r="I89" s="15" t="s">
-        <v>1371</v>
-      </c>
-      <c r="J89" s="16" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A90" s="28" t="s">
-        <v>1373</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C90" s="28" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D90" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
-      <c r="H90" s="14"/>
-      <c r="I90" s="15" t="s">
-        <v>1374</v>
-      </c>
-      <c r="J90" s="16" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A91" s="28" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C91" s="28" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
-      <c r="H91" s="14"/>
-      <c r="I91" s="26" t="s">
-        <v>1377</v>
-      </c>
-      <c r="J91" s="27" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="28" t="s">
-        <v>1379</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C92" s="28" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="14"/>
-      <c r="I92" s="15" t="s">
-        <v>1380</v>
-      </c>
-      <c r="J92" s="16" t="s">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A93" s="13" t="s">
-        <v>1382</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C93" s="28" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
-      <c r="I93" s="26" t="s">
-        <v>1383</v>
-      </c>
-      <c r="J93" s="27" t="s">
-        <v>1384</v>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10" t="s">
+        <v>911</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>912</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I40" r:id="rId1" xr:uid="{B6B3115E-1E2F-4686-A276-69FF06A4F1A9}"/>
-    <hyperlink ref="I42" r:id="rId2" xr:uid="{FE61C9A3-EE64-45FD-A959-325143632462}"/>
-    <hyperlink ref="I43" r:id="rId3" xr:uid="{24429794-FD58-4048-872D-F52CDFFDA24C}"/>
-    <hyperlink ref="I45" r:id="rId4" xr:uid="{F11B6C33-A55F-4DCF-AD91-F1D0AFD9CE66}"/>
-    <hyperlink ref="I46" r:id="rId5" xr:uid="{EC92489F-E8A5-4E5C-B956-A48B35D22B64}"/>
-    <hyperlink ref="I48" r:id="rId6" xr:uid="{5FE6D4B7-4E1F-4589-9C72-9BA6D9059A5A}"/>
-    <hyperlink ref="I72" r:id="rId7" xr:uid="{694897C7-F8C1-4384-86EB-08A1B5E6503C}"/>
-    <hyperlink ref="I82" r:id="rId8" xr:uid="{318963CF-F377-495B-BE33-41EACC747CD7}"/>
-    <hyperlink ref="I83" r:id="rId9" xr:uid="{43EBE0C7-D999-4D7F-8DD0-CA1037EAC4AA}"/>
-    <hyperlink ref="I86" r:id="rId10" xr:uid="{E9039FBE-7C9B-4910-AF6D-E17DF77E261E}"/>
-    <hyperlink ref="I87" r:id="rId11" xr:uid="{8EBD1083-F485-48FC-BCE3-F988335E84A7}"/>
-    <hyperlink ref="I88" r:id="rId12" xr:uid="{A52501E0-E3A2-4CFE-9C58-F8370E8D0787}"/>
-    <hyperlink ref="I2" r:id="rId13" xr:uid="{8D4C6B70-FAB8-4E6B-AD66-9C2965F5E699}"/>
-    <hyperlink ref="I89" r:id="rId14" xr:uid="{A66857AA-510F-4D0B-ADDE-6DCF6BBFBA98}"/>
-    <hyperlink ref="I93" r:id="rId15" xr:uid="{10C13673-A455-4470-AE7C-718EEA89FF2C}"/>
-    <hyperlink ref="I92" r:id="rId16" xr:uid="{CB946A84-9611-4013-8B3D-027D69D28FF0}"/>
-    <hyperlink ref="I91" r:id="rId17" xr:uid="{B5D4026A-6A7C-41B1-B023-EA1477696E4A}"/>
-    <hyperlink ref="I90" r:id="rId18" xr:uid="{D028923D-576F-441D-BC8C-E6280FC34BAD}"/>
-    <hyperlink ref="I19" r:id="rId19" xr:uid="{6CBF631D-4D8C-4D4A-B943-7C1FB826B21B}"/>
-    <hyperlink ref="I20" r:id="rId20" xr:uid="{F4A977E1-0867-40D6-BDC7-0B7B6B3BB98B}"/>
-    <hyperlink ref="I21" r:id="rId21" xr:uid="{B4D9B2C4-14E0-4503-BE95-C1C24D8DE16E}"/>
-    <hyperlink ref="I22" r:id="rId22" xr:uid="{9338B7EA-73A0-4A98-9C0E-0C50F3F7CA78}"/>
-    <hyperlink ref="I23" r:id="rId23" xr:uid="{ECBFB55D-7CE3-498F-950A-A609D5DAA670}"/>
-    <hyperlink ref="I24" r:id="rId24" xr:uid="{749CD73E-06C9-4C15-98A3-4CE25A84DBF3}"/>
-    <hyperlink ref="I25" r:id="rId25" xr:uid="{7CB36453-3486-462C-A86D-E24FAA1C135D}"/>
-    <hyperlink ref="I26" r:id="rId26" xr:uid="{6FD65289-02AD-4E0D-943D-1D1B063D0710}"/>
-    <hyperlink ref="I31" r:id="rId27" xr:uid="{B72DEEAD-F615-4CBA-B334-CE992FE1B159}"/>
-    <hyperlink ref="I32" r:id="rId28" xr:uid="{C4C1571D-1DAC-46B0-ABB3-7ED2E866B626}"/>
-    <hyperlink ref="I7" r:id="rId29" xr:uid="{B12E52D2-1BDE-4771-9D50-8CC27BF79833}"/>
-    <hyperlink ref="I8" r:id="rId30" xr:uid="{AE2C73E9-AECC-487D-A5FA-29B89DBDC129}"/>
-    <hyperlink ref="I9" r:id="rId31" xr:uid="{D86510BA-0C93-4EA1-A9BD-C86D5F2BBE91}"/>
-    <hyperlink ref="I10" r:id="rId32" xr:uid="{8B9B1D60-2051-46F5-A226-F8F43E6C3151}"/>
-    <hyperlink ref="I11" r:id="rId33" xr:uid="{5CC90BF9-8057-473D-8324-403D055924EC}"/>
-    <hyperlink ref="I12" r:id="rId34" xr:uid="{A76F3B12-3D32-4298-82CE-D820B8384CDC}"/>
-    <hyperlink ref="I3" r:id="rId35" xr:uid="{4AD2F4BA-90E3-4D07-A795-3C7880496846}"/>
-    <hyperlink ref="I13" r:id="rId36" xr:uid="{937BCFED-76DA-4902-8A3F-0BE5C64A3BFA}"/>
-    <hyperlink ref="I14" r:id="rId37" xr:uid="{6E78079C-4CFD-4E23-924A-929B83424233}"/>
-    <hyperlink ref="I15" r:id="rId38" xr:uid="{A971A5E8-1F9F-4DC7-9244-4FBBFBDDC614}"/>
-    <hyperlink ref="I5" r:id="rId39" xr:uid="{549CCC20-CD18-4842-B73C-D3FB638EC59E}"/>
-    <hyperlink ref="I4" r:id="rId40" xr:uid="{DE2C496B-BE40-45E2-AB76-33DDAB9DE5DE}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart r:id="rId41"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="46" customWidth="1"/>
+    <col min="10" max="10" width="196.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>880</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="16" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="19" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>880</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20" t="s">
+        <v>1232</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="22" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>880</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J20" s="24" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="27" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="29" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="31"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="25" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>880</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="27" t="s">
+        <v>1242</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11" t="s">
+        <v>884</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>886</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11" t="s">
+        <v>887</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>889</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11" t="s">
+        <v>890</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>892</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
+        <v>904</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10" t="s">
+        <v>905</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
+        <v>907</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>908</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10" t="s">
+        <v>911</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I17" r:id="rId1" xr:uid="{9B084770-82E4-4C2F-BB73-1026CC166C8F}"/>
+    <hyperlink ref="I18" r:id="rId2" xr:uid="{84C1E994-9822-4DA4-82EC-77E0C3A22C65}"/>
+    <hyperlink ref="I20" r:id="rId3" xr:uid="{D271BD98-633B-40A5-ABD8-541E13FCDE87}"/>
+    <hyperlink ref="I21" r:id="rId4" xr:uid="{9760039F-55FD-4E49-9DCC-DAB8F932008D}"/>
+    <hyperlink ref="I23" r:id="rId5" xr:uid="{ED8919F5-CC95-46F6-BF2C-F21A73C799E4}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J132"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -21059,7 +20048,7 @@
     </row>
     <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>70</v>
@@ -21077,15 +20066,15 @@
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>70</v>
@@ -21095,7 +20084,7 @@
         <v>48</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>74</v>
@@ -21105,21 +20094,21 @@
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>48</v>
@@ -21129,21 +20118,21 @@
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>48</v>
@@ -21153,21 +20142,21 @@
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>54</v>
@@ -21180,24 +20169,24 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>54</v>
@@ -21211,21 +20200,21 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>54</v>
@@ -21238,24 +20227,24 @@
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>54</v>
@@ -21269,21 +20258,21 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>54</v>
@@ -21297,21 +20286,21 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>48</v>
@@ -21321,21 +20310,21 @@
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>54</v>
@@ -21349,21 +20338,21 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>941</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>935</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>54</v>
@@ -21377,21 +20366,21 @@
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>54</v>
@@ -21405,21 +20394,21 @@
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>54</v>
@@ -21433,21 +20422,21 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>48</v>
@@ -21457,21 +20446,21 @@
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>54</v>
@@ -21485,21 +20474,21 @@
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
+        <v>962</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>956</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>950</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>54</v>
@@ -21512,24 +20501,24 @@
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="10" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>54</v>
@@ -21542,24 +20531,24 @@
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>54</v>
@@ -21573,21 +20562,21 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>54</v>
@@ -21600,24 +20589,24 @@
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>48</v>
@@ -21627,21 +20616,21 @@
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>54</v>
@@ -21654,24 +20643,24 @@
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>54</v>
@@ -21685,21 +20674,21 @@
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>54</v>
@@ -21712,24 +20701,24 @@
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>54</v>
@@ -21742,24 +20731,24 @@
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>54</v>
@@ -21773,21 +20762,21 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>48</v>
@@ -21797,21 +20786,21 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>54</v>
@@ -21825,21 +20814,21 @@
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>995</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>989</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>54</v>
@@ -21853,21 +20842,21 @@
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
       <c r="I30" s="10" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>54</v>
@@ -21881,21 +20870,21 @@
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
       <c r="I31" s="10" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>54</v>
@@ -21909,21 +20898,21 @@
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>54</v>
@@ -21936,24 +20925,24 @@
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>54</v>
@@ -21967,21 +20956,21 @@
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>54</v>
@@ -21995,21 +20984,21 @@
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>48</v>
@@ -22019,21 +21008,21 @@
       <c r="G36" s="11"/>
       <c r="H36" s="11"/>
       <c r="I36" s="11" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>54</v>
@@ -22047,21 +21036,21 @@
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>1019</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>1013</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>54</v>
@@ -22075,21 +21064,21 @@
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>54</v>
@@ -22102,30 +21091,30 @@
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>74</v>
@@ -22133,21 +21122,21 @@
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>54</v>
@@ -22161,21 +21150,21 @@
       <c r="G41" s="10"/>
       <c r="H41" s="10"/>
       <c r="I41" s="10" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>54</v>
@@ -22189,21 +21178,21 @@
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>48</v>
@@ -22213,21 +21202,21 @@
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>54</v>
@@ -22241,21 +21230,21 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>54</v>
@@ -22268,24 +21257,24 @@
       </c>
       <c r="G45" s="10"/>
       <c r="H45" s="10" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>1035</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>1029</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>54</v>
@@ -22299,21 +21288,21 @@
       <c r="G46" s="10"/>
       <c r="H46" s="10"/>
       <c r="I46" s="10" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>54</v>
@@ -22327,21 +21316,21 @@
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>54</v>
@@ -22355,21 +21344,21 @@
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
       <c r="I48" s="10" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>54</v>
@@ -22383,21 +21372,21 @@
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
       <c r="I49" s="10" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>54</v>
@@ -22410,24 +21399,24 @@
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>54</v>
@@ -22441,21 +21430,21 @@
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
       <c r="I51" s="10" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>54</v>
@@ -22469,21 +21458,21 @@
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
       <c r="I52" s="10" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>48</v>
@@ -22493,21 +21482,21 @@
       <c r="G53" s="11"/>
       <c r="H53" s="11"/>
       <c r="I53" s="11" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>54</v>
@@ -22521,21 +21510,21 @@
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
       <c r="I54" s="10" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="10" t="s">
         <v>1047</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>1041</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>54</v>
@@ -22549,21 +21538,21 @@
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
       <c r="I55" s="10" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>54</v>
@@ -22577,21 +21566,21 @@
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
       <c r="I56" s="10" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>54</v>
@@ -22604,13 +21593,13 @@
       </c>
       <c r="G57" s="10"/>
       <c r="H57" s="10" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
@@ -22621,7 +21610,7 @@
         <v>70</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>54</v>
@@ -22637,13 +21626,13 @@
     </row>
     <row r="59" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>54</v>
@@ -22657,21 +21646,21 @@
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
       <c r="I59" s="10" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>54</v>
@@ -22685,21 +21674,21 @@
       <c r="G60" s="10"/>
       <c r="H60" s="10"/>
       <c r="I60" s="10" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="11" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>48</v>
@@ -22709,21 +21698,21 @@
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
       <c r="I61" s="11" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>54</v>
@@ -22737,21 +21726,21 @@
       <c r="G62" s="10"/>
       <c r="H62" s="10"/>
       <c r="I62" s="10" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>1063</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>1057</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>54</v>
@@ -22764,24 +21753,24 @@
       </c>
       <c r="G63" s="10"/>
       <c r="H63" s="10" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>54</v>
@@ -22794,24 +21783,24 @@
       </c>
       <c r="G64" s="10"/>
       <c r="H64" s="10" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>54</v>
@@ -22825,21 +21814,21 @@
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
       <c r="I65" s="10" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>54</v>
@@ -22853,21 +21842,21 @@
       <c r="G66" s="10"/>
       <c r="H66" s="10"/>
       <c r="I66" s="10" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>54</v>
@@ -22881,21 +21870,21 @@
       <c r="G67" s="10"/>
       <c r="H67" s="10"/>
       <c r="I67" s="10" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>54</v>
@@ -22909,21 +21898,21 @@
       <c r="G68" s="10"/>
       <c r="H68" s="10"/>
       <c r="I68" s="10" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>54</v>
@@ -22937,21 +21926,21 @@
       <c r="G69" s="10"/>
       <c r="H69" s="10"/>
       <c r="I69" s="10" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>54</v>
@@ -22965,21 +21954,21 @@
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
       <c r="I70" s="10" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>48</v>
@@ -22989,21 +21978,21 @@
       <c r="G71" s="11"/>
       <c r="H71" s="11"/>
       <c r="I71" s="11" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>54</v>
@@ -23017,27 +22006,27 @@
       <c r="G72" s="10"/>
       <c r="H72" s="10"/>
       <c r="I72" s="10" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>1088</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>1082</v>
-      </c>
       <c r="D73" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>74</v>
@@ -23045,21 +22034,21 @@
       <c r="G73" s="10"/>
       <c r="H73" s="10"/>
       <c r="I73" s="10" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>54</v>
@@ -23073,21 +22062,21 @@
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
       <c r="I74" s="10" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>54</v>
@@ -23100,24 +22089,24 @@
       </c>
       <c r="G75" s="10"/>
       <c r="H75" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>54</v>
@@ -23131,21 +22120,21 @@
       <c r="G76" s="10"/>
       <c r="H76" s="10"/>
       <c r="I76" s="10" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>54</v>
@@ -23159,21 +22148,21 @@
       <c r="G77" s="10"/>
       <c r="H77" s="10"/>
       <c r="I77" s="10" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>54</v>
@@ -23186,24 +22175,24 @@
       </c>
       <c r="G78" s="10"/>
       <c r="H78" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>54</v>
@@ -23217,21 +22206,21 @@
       <c r="G79" s="10"/>
       <c r="H79" s="10"/>
       <c r="I79" s="10" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>54</v>
@@ -23245,21 +22234,21 @@
       <c r="G80" s="10"/>
       <c r="H80" s="10"/>
       <c r="I80" s="10" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" s="11" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>48</v>
@@ -23269,21 +22258,21 @@
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
       <c r="I81" s="11" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>54</v>
@@ -23297,21 +22286,21 @@
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
       <c r="I82" s="10" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C83" s="10" t="s">
         <v>1103</v>
-      </c>
-      <c r="B83" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>1097</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>54</v>
@@ -23324,24 +22313,24 @@
       </c>
       <c r="G83" s="10"/>
       <c r="H83" s="10" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>54</v>
@@ -23355,21 +22344,21 @@
       <c r="G84" s="10"/>
       <c r="H84" s="10"/>
       <c r="I84" s="10" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>54</v>
@@ -23382,24 +22371,24 @@
       </c>
       <c r="G85" s="10"/>
       <c r="H85" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>54</v>
@@ -23412,24 +22401,24 @@
       </c>
       <c r="G86" s="10"/>
       <c r="H86" s="10" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>54</v>
@@ -23443,21 +22432,21 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="10" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>54</v>
@@ -23471,21 +22460,21 @@
       <c r="G88" s="10"/>
       <c r="H88" s="10"/>
       <c r="I88" s="10" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>54</v>
@@ -23499,21 +22488,21 @@
       <c r="G89" s="10"/>
       <c r="H89" s="10"/>
       <c r="I89" s="10" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" s="11" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>48</v>
@@ -23523,21 +22512,21 @@
       <c r="G90" s="11"/>
       <c r="H90" s="11"/>
       <c r="I90" s="11" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>54</v>
@@ -23551,21 +22540,21 @@
       <c r="G91" s="10"/>
       <c r="H91" s="10"/>
       <c r="I91" s="10" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C92" s="10" t="s">
         <v>1126</v>
-      </c>
-      <c r="B92" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>1120</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>54</v>
@@ -23579,21 +22568,21 @@
       <c r="G92" s="10"/>
       <c r="H92" s="10"/>
       <c r="I92" s="10" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>54</v>
@@ -23606,24 +22595,24 @@
       </c>
       <c r="G93" s="10"/>
       <c r="H93" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>54</v>
@@ -23637,21 +22626,21 @@
       <c r="G94" s="10"/>
       <c r="H94" s="10"/>
       <c r="I94" s="10" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>54</v>
@@ -23664,30 +22653,30 @@
       </c>
       <c r="G95" s="10"/>
       <c r="H95" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="F96" s="10" t="s">
         <v>74</v>
@@ -23695,21 +22684,21 @@
       <c r="G96" s="10"/>
       <c r="H96" s="10"/>
       <c r="I96" s="10" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>54</v>
@@ -23722,24 +22711,24 @@
       </c>
       <c r="G97" s="10"/>
       <c r="H97" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>54</v>
@@ -23753,21 +22742,21 @@
       <c r="G98" s="10"/>
       <c r="H98" s="10"/>
       <c r="I98" s="10" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>54</v>
@@ -23781,21 +22770,21 @@
       <c r="G99" s="10"/>
       <c r="H99" s="10"/>
       <c r="I99" s="10" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>54</v>
@@ -23808,24 +22797,24 @@
       </c>
       <c r="G100" s="10"/>
       <c r="H100" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>54</v>
@@ -23839,21 +22828,21 @@
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
       <c r="I101" s="10" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>54</v>
@@ -23867,10 +22856,10 @@
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
       <c r="I102" s="10" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
@@ -23885,19 +22874,19 @@
         <v>48</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="9"/>
       <c r="J103" s="9" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A104" s="11" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>103</v>
@@ -23916,18 +22905,18 @@
         <v>123</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A105" s="11" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>48</v>
@@ -23937,21 +22926,21 @@
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
       <c r="I105" s="11" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>54</v>
@@ -23965,21 +22954,21 @@
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
       <c r="I106" s="10" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>54</v>
@@ -23992,24 +22981,24 @@
       </c>
       <c r="G107" s="10"/>
       <c r="H107" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>54</v>
@@ -24023,21 +23012,21 @@
       <c r="G108" s="10"/>
       <c r="H108" s="10"/>
       <c r="I108" s="10" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C109" s="10" t="s">
         <v>1153</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>1147</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>54</v>
@@ -24051,27 +23040,27 @@
       <c r="G109" s="10"/>
       <c r="H109" s="10"/>
       <c r="I109" s="10" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="F110" s="10" t="s">
         <v>74</v>
@@ -24079,21 +23068,21 @@
       <c r="G110" s="10"/>
       <c r="H110" s="10"/>
       <c r="I110" s="10" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>54</v>
@@ -24106,24 +23095,24 @@
       </c>
       <c r="G111" s="10"/>
       <c r="H111" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>48</v>
@@ -24133,21 +23122,21 @@
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
       <c r="I112" s="11" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>54</v>
@@ -24161,21 +23150,21 @@
       <c r="G113" s="10"/>
       <c r="H113" s="10"/>
       <c r="I113" s="10" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C114" s="10" t="s">
         <v>1168</v>
-      </c>
-      <c r="B114" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>1162</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>54</v>
@@ -24188,24 +23177,24 @@
       </c>
       <c r="G114" s="10"/>
       <c r="H114" s="10" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>54</v>
@@ -24218,24 +23207,24 @@
       </c>
       <c r="G115" s="10"/>
       <c r="H115" s="10" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>54</v>
@@ -24249,21 +23238,21 @@
       <c r="G116" s="10"/>
       <c r="H116" s="10"/>
       <c r="I116" s="10" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>54</v>
@@ -24277,21 +23266,21 @@
       <c r="G117" s="10"/>
       <c r="H117" s="10"/>
       <c r="I117" s="10" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A118" s="11" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="D118" s="11" t="s">
         <v>48</v>
@@ -24301,21 +23290,21 @@
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
       <c r="I118" s="11" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>54</v>
@@ -24329,21 +23318,21 @@
       <c r="G119" s="10"/>
       <c r="H119" s="10"/>
       <c r="I119" s="10" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C120" s="10" t="s">
         <v>1188</v>
-      </c>
-      <c r="B120" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>1182</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>54</v>
@@ -24357,10 +23346,10 @@
       <c r="G120" s="10"/>
       <c r="H120" s="10"/>
       <c r="I120" s="10" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.35">
@@ -24371,7 +23360,7 @@
         <v>70</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>54</v>
@@ -24387,13 +23376,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>54</v>
@@ -24409,13 +23398,13 @@
     </row>
     <row r="123" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="D123" s="10" t="s">
         <v>54</v>
@@ -24429,21 +23418,21 @@
       <c r="G123" s="10"/>
       <c r="H123" s="10"/>
       <c r="I123" s="10" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="D124" s="10" t="s">
         <v>54</v>
@@ -24456,24 +23445,24 @@
       </c>
       <c r="G124" s="10"/>
       <c r="H124" s="10" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A125" s="11" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="D125" s="11" t="s">
         <v>48</v>
@@ -24483,21 +23472,21 @@
       <c r="G125" s="11"/>
       <c r="H125" s="11"/>
       <c r="I125" s="11" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="J125" s="11" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>54</v>
@@ -24511,21 +23500,21 @@
       <c r="G126" s="10"/>
       <c r="H126" s="10"/>
       <c r="I126" s="10" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B127" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C127" s="10" t="s">
         <v>1204</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C127" s="10" t="s">
-        <v>1198</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>54</v>
@@ -24539,10 +23528,10 @@
       <c r="G127" s="10"/>
       <c r="H127" s="10"/>
       <c r="I127" s="10" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.35">
@@ -24553,7 +23542,7 @@
         <v>70</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>54</v>
@@ -24569,13 +23558,13 @@
     </row>
     <row r="129" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="B129" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="D129" s="10" t="s">
         <v>54</v>
@@ -24589,21 +23578,21 @@
       <c r="G129" s="10"/>
       <c r="H129" s="10"/>
       <c r="I129" s="10" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="B130" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>54</v>
@@ -24617,21 +23606,21 @@
       <c r="G130" s="10"/>
       <c r="H130" s="10"/>
       <c r="I130" s="10" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B131" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="D131" s="10" t="s">
         <v>54</v>
@@ -24645,21 +23634,21 @@
       <c r="G131" s="10"/>
       <c r="H131" s="10"/>
       <c r="I131" s="10" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="B132" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="D132" s="10" t="s">
         <v>54</v>
@@ -24673,10 +23662,10 @@
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
       <c r="I132" s="10" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
     </row>
   </sheetData>

--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="104" documentId="11_A69C58C6367E2462DB23AA295C848E29977FB4C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5C7BAAD-81F3-4468-87EF-C5AB2AC1C95D}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="11_A69C58C6367E2462DB23AA295C848E29977FB4C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0453C2AE-A2D5-4EED-AA0D-44C3F02D42EE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18221,7 +18221,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -19263,11 +19263,6 @@
       </c>
       <c r="J40" t="s">
         <v>942</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
